--- a/docs/宝可梦图鉴.xlsx
+++ b/docs/宝可梦图鉴.xlsx
@@ -5533,7 +5533,7 @@
       </c>
       <c r="H2" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I2" s="23" t="n">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="H3" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I3" s="23" t="n">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H4" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I4" s="23" t="n">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I5" s="23" t="n">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I6" s="23" t="n">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I7" s="23" t="n">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I8" s="23" t="n">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I9" s="23" t="n">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I10" s="23" t="n">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I11" s="23" t="n">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>陆上、龙群</t>
+          <t>陆上群、龙群</t>
         </is>
       </c>
       <c r="I27" s="23" t="n">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>陆上、龙群</t>
+          <t>陆上群、龙群</t>
         </is>
       </c>
       <c r="I28" s="23" t="n">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I29" s="23" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I30" s="23" t="n">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I31" s="23" t="n">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="H36" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I36" s="23" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="H39" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I39" s="23" t="n">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="H40" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I40" s="23" t="n">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="H41" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I41" s="23" t="n">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="H55" s="23" t="inlineStr">
         <is>
-          <t>虫、植物群</t>
+          <t>虫群、植物群</t>
         </is>
       </c>
       <c r="I55" s="23" t="n">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="H56" s="23" t="inlineStr">
         <is>
-          <t>虫、植物群</t>
+          <t>虫群、植物群</t>
         </is>
       </c>
       <c r="I56" s="23" t="n">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="H68" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I68" s="23" t="n">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="H69" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I69" s="23" t="n">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="H100" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I100" s="23" t="n">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="H101" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I101" s="23" t="n">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="H102" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I102" s="23" t="n">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="H103" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I103" s="23" t="n">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="H106" s="23" t="inlineStr">
         <is>
-          <t>飞行、陆上群</t>
+          <t>飞行群、陆上群</t>
         </is>
       </c>
       <c r="I106" s="23" t="n">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="H107" s="23" t="inlineStr">
         <is>
-          <t>飞行、陆上群</t>
+          <t>飞行群、陆上群</t>
         </is>
       </c>
       <c r="I107" s="23" t="n">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="H110" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I110" s="23" t="n">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H111" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I111" s="23" t="n">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="H142" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I142" s="23" t="n">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="H143" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I143" s="23" t="n">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="H147" s="23" t="inlineStr">
         <is>
-          <t>水中1、龙群</t>
+          <t>水中1群、龙群</t>
         </is>
       </c>
       <c r="I147" s="23" t="n">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="H148" s="23" t="inlineStr">
         <is>
-          <t>水中1、龙群</t>
+          <t>水中1群、龙群</t>
         </is>
       </c>
       <c r="I148" s="23" t="n">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="H164" s="23" t="inlineStr">
         <is>
-          <t>水中2、龙群</t>
+          <t>水中2群、龙群</t>
         </is>
       </c>
       <c r="I164" s="23" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="H165" s="23" t="inlineStr">
         <is>
-          <t>水中2、龙群</t>
+          <t>水中2群、龙群</t>
         </is>
       </c>
       <c r="I165" s="23" t="n">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="H166" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I166" s="23" t="n">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="H173" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I173" s="23" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="H174" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I174" s="23" t="n">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="H175" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I175" s="23" t="n">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="H176" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I176" s="23" t="n">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="H185" s="23" t="inlineStr">
         <is>
-          <t>水中1、龙群</t>
+          <t>水中1群、龙群</t>
         </is>
       </c>
       <c r="I185" s="23" t="n">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="H186" s="23" t="inlineStr">
         <is>
-          <t>水中1、龙群</t>
+          <t>水中1群、龙群</t>
         </is>
       </c>
       <c r="I186" s="23" t="n">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="H187" s="23" t="inlineStr">
         <is>
-          <t>水中1、龙群</t>
+          <t>水中1群、龙群</t>
         </is>
       </c>
       <c r="I187" s="23" t="n">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="H190" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I190" s="23" t="n">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="H191" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I191" s="23" t="n">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="H192" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I192" s="23" t="n">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="H197" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I197" s="23" t="n">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="H198" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I198" s="23" t="n">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="H199" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I199" s="23" t="n">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="H215" s="23" t="inlineStr">
         <is>
-          <t>飞行、妖精群</t>
+          <t>飞行群、妖精群</t>
         </is>
       </c>
       <c r="I215" s="23" t="n">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="H218" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I218" s="23" t="n">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="H219" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I219" s="23" t="n">
@@ -18775,7 +18775,7 @@
       </c>
       <c r="H220" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I220" s="23" t="n">
@@ -18897,7 +18897,7 @@
       </c>
       <c r="H222" s="23" t="inlineStr">
         <is>
-          <t>水中1、妖精群</t>
+          <t>水中1群、妖精群</t>
         </is>
       </c>
       <c r="I222" s="23" t="n">
@@ -18958,7 +18958,7 @@
       </c>
       <c r="H223" s="23" t="inlineStr">
         <is>
-          <t>水中1、妖精群</t>
+          <t>水中1群、妖精群</t>
         </is>
       </c>
       <c r="I223" s="23" t="n">
@@ -19141,7 +19141,7 @@
       </c>
       <c r="H226" s="23" t="inlineStr">
         <is>
-          <t>妖精、植物群</t>
+          <t>妖精群、植物群</t>
         </is>
       </c>
       <c r="I226" s="23" t="n">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="H227" s="23" t="inlineStr">
         <is>
-          <t>妖精、植物群</t>
+          <t>妖精群、植物群</t>
         </is>
       </c>
       <c r="I227" s="23" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="H228" s="23" t="inlineStr">
         <is>
-          <t>妖精、植物群</t>
+          <t>妖精群、植物群</t>
         </is>
       </c>
       <c r="I228" s="23" t="n">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="H233" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I233" s="23" t="n">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="H234" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I234" s="23" t="n">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="H235" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I235" s="23" t="n">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="H239" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I239" s="23" t="n">
@@ -19995,7 +19995,7 @@
       </c>
       <c r="H240" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I240" s="23" t="n">
@@ -22140,7 +22140,7 @@
       </c>
       <c r="H277" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I277" s="23" t="n">
@@ -22201,7 +22201,7 @@
       </c>
       <c r="H278" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I278" s="23" t="n">
@@ -23055,7 +23055,7 @@
       </c>
       <c r="H292" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I292" s="23" t="n">
@@ -23116,7 +23116,7 @@
       </c>
       <c r="H293" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I293" s="23" t="n">
@@ -23177,7 +23177,7 @@
       </c>
       <c r="H294" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中2群</t>
+          <t>水中1群、水中2群</t>
         </is>
       </c>
       <c r="I294" s="23" t="n">
@@ -23238,7 +23238,7 @@
       </c>
       <c r="H295" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中2群</t>
+          <t>水中1群、水中2群</t>
         </is>
       </c>
       <c r="I295" s="23" t="n">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="H296" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I296" s="23" t="n">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="H301" s="23" t="inlineStr">
         <is>
-          <t>水中1、龙群</t>
+          <t>水中1群、龙群</t>
         </is>
       </c>
       <c r="I301" s="23" t="n">
@@ -24906,7 +24906,7 @@
       </c>
       <c r="H323" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I323" s="23" t="n">
@@ -24967,7 +24967,7 @@
       </c>
       <c r="H324" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I324" s="23" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="H325" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I325" s="23" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="H329" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I329" s="23" t="n">
@@ -25333,7 +25333,7 @@
       </c>
       <c r="H330" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I330" s="23" t="n">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="H331" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I331" s="23" t="n">
@@ -26126,7 +26126,7 @@
       </c>
       <c r="H343" s="23" t="inlineStr">
         <is>
-          <t>水中1、植物群</t>
+          <t>水中1群、植物群</t>
         </is>
       </c>
       <c r="I343" s="23" t="n">
@@ -26187,7 +26187,7 @@
       </c>
       <c r="H344" s="23" t="inlineStr">
         <is>
-          <t>水中1、植物群</t>
+          <t>水中1群、植物群</t>
         </is>
       </c>
       <c r="I344" s="23" t="n">
@@ -26248,7 +26248,7 @@
       </c>
       <c r="H345" s="23" t="inlineStr">
         <is>
-          <t>水中1、植物群</t>
+          <t>水中1群、植物群</t>
         </is>
       </c>
       <c r="I345" s="23" t="n">
@@ -26309,7 +26309,7 @@
       </c>
       <c r="H346" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I346" s="23" t="n">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="H347" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I347" s="23" t="n">
@@ -26431,7 +26431,7 @@
       </c>
       <c r="H348" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I348" s="23" t="n">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="H351" s="23" t="inlineStr">
         <is>
-          <t>水中1、飞行群</t>
+          <t>水中1群、飞行群</t>
         </is>
       </c>
       <c r="I351" s="23" t="n">
@@ -26675,7 +26675,7 @@
       </c>
       <c r="H352" s="23" t="inlineStr">
         <is>
-          <t>水中1、飞行群</t>
+          <t>水中1群、飞行群</t>
         </is>
       </c>
       <c r="I352" s="23" t="n">
@@ -26736,7 +26736,7 @@
       </c>
       <c r="H353" s="23" t="inlineStr">
         <is>
-          <t>人型、不定形群</t>
+          <t>人型群、不定形群</t>
         </is>
       </c>
       <c r="I353" s="23" t="n">
@@ -26797,7 +26797,7 @@
       </c>
       <c r="H354" s="23" t="inlineStr">
         <is>
-          <t>人型、不定形群</t>
+          <t>人型群、不定形群</t>
         </is>
       </c>
       <c r="I354" s="23" t="n">
@@ -26858,7 +26858,7 @@
       </c>
       <c r="H355" s="23" t="inlineStr">
         <is>
-          <t>人型、不定形群</t>
+          <t>人型群、不定形群</t>
         </is>
       </c>
       <c r="I355" s="23" t="n">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="H356" s="23" t="inlineStr">
         <is>
-          <t>水中1、虫群</t>
+          <t>水中1群、虫群</t>
         </is>
       </c>
       <c r="I356" s="23" t="n">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="H357" s="23" t="inlineStr">
         <is>
-          <t>水中1、虫群</t>
+          <t>水中1群、虫群</t>
         </is>
       </c>
       <c r="I357" s="23" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="H358" s="23" t="inlineStr">
         <is>
-          <t>妖精、植物群</t>
+          <t>妖精群、植物群</t>
         </is>
       </c>
       <c r="I358" s="23" t="n">
@@ -27102,7 +27102,7 @@
       </c>
       <c r="H359" s="23" t="inlineStr">
         <is>
-          <t>妖精、植物群</t>
+          <t>妖精群、植物群</t>
         </is>
       </c>
       <c r="I359" s="23" t="n">
@@ -27529,7 +27529,7 @@
       </c>
       <c r="H366" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I366" s="23" t="n">
@@ -27590,7 +27590,7 @@
       </c>
       <c r="H367" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I367" s="23" t="n">
@@ -27651,7 +27651,7 @@
       </c>
       <c r="H368" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I368" s="23" t="n">
@@ -27952,7 +27952,7 @@
       </c>
       <c r="H373" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I373" s="23" t="n">
@@ -28013,7 +28013,7 @@
       </c>
       <c r="H374" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I374" s="23" t="n">
@@ -28135,7 +28135,7 @@
       </c>
       <c r="H376" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I376" s="23" t="n">
@@ -28745,7 +28745,7 @@
       </c>
       <c r="H386" s="23" t="inlineStr">
         <is>
-          <t>虫、人型群</t>
+          <t>虫群、人型群</t>
         </is>
       </c>
       <c r="I386" s="23" t="n">
@@ -28806,7 +28806,7 @@
       </c>
       <c r="H387" s="23" t="inlineStr">
         <is>
-          <t>虫、人型群</t>
+          <t>虫群、人型群</t>
         </is>
       </c>
       <c r="I387" s="23" t="n">
@@ -28867,7 +28867,7 @@
       </c>
       <c r="H388" s="23" t="inlineStr">
         <is>
-          <t>妖精、植物群</t>
+          <t>妖精群、植物群</t>
         </is>
       </c>
       <c r="I388" s="23" t="n">
@@ -29172,7 +29172,7 @@
       </c>
       <c r="H393" s="23" t="inlineStr">
         <is>
-          <t>陆上、水中2群</t>
+          <t>陆上群、水中2群</t>
         </is>
       </c>
       <c r="I393" s="23" t="n">
@@ -29233,7 +29233,7 @@
       </c>
       <c r="H394" s="23" t="inlineStr">
         <is>
-          <t>陆上、水中2群</t>
+          <t>陆上群、水中2群</t>
         </is>
       </c>
       <c r="I394" s="23" t="n">
@@ -29599,7 +29599,7 @@
       </c>
       <c r="H400" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I400" s="23" t="n">
@@ -29660,7 +29660,7 @@
       </c>
       <c r="H401" s="23" t="inlineStr">
         <is>
-          <t>虫、龙群</t>
+          <t>虫群、龙群</t>
         </is>
       </c>
       <c r="I401" s="23" t="n">
@@ -29721,7 +29721,7 @@
       </c>
       <c r="H402" s="23" t="inlineStr">
         <is>
-          <t>虫、龙群</t>
+          <t>虫群、龙群</t>
         </is>
       </c>
       <c r="I402" s="23" t="n">
@@ -29782,7 +29782,7 @@
       </c>
       <c r="H403" s="23" t="inlineStr">
         <is>
-          <t>虫、龙群</t>
+          <t>虫群、龙群</t>
         </is>
       </c>
       <c r="I403" s="23" t="n">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="H404" s="23" t="inlineStr">
         <is>
-          <t>植物、人型群</t>
+          <t>植物群、人型群</t>
         </is>
       </c>
       <c r="I404" s="23" t="n">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="H405" s="23" t="inlineStr">
         <is>
-          <t>植物、人型群</t>
+          <t>植物群、人型群</t>
         </is>
       </c>
       <c r="I405" s="23" t="n">
@@ -29965,7 +29965,7 @@
       </c>
       <c r="H406" s="23" t="inlineStr">
         <is>
-          <t>飞行、龙群</t>
+          <t>飞行群、龙群</t>
         </is>
       </c>
       <c r="I406" s="23" t="n">
@@ -30026,7 +30026,7 @@
       </c>
       <c r="H407" s="23" t="inlineStr">
         <is>
-          <t>飞行、龙群</t>
+          <t>飞行群、龙群</t>
         </is>
       </c>
       <c r="I407" s="23" t="n">
@@ -30148,7 +30148,7 @@
       </c>
       <c r="H409" s="23" t="inlineStr">
         <is>
-          <t>陆上、龙群</t>
+          <t>陆上群、龙群</t>
         </is>
       </c>
       <c r="I409" s="23" t="n">
@@ -30453,7 +30453,7 @@
       </c>
       <c r="H414" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I414" s="23" t="n">
@@ -30514,7 +30514,7 @@
       </c>
       <c r="H415" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I415" s="23" t="n">
@@ -30941,7 +30941,7 @@
       </c>
       <c r="H422" s="23" t="inlineStr">
         <is>
-          <t>水中1、龙群</t>
+          <t>水中1群、龙群</t>
         </is>
       </c>
       <c r="I422" s="23" t="n">
@@ -31002,7 +31002,7 @@
       </c>
       <c r="H423" s="23" t="inlineStr">
         <is>
-          <t>水中1、龙群</t>
+          <t>水中1群、龙群</t>
         </is>
       </c>
       <c r="I423" s="23" t="n">
@@ -31063,7 +31063,7 @@
       </c>
       <c r="H424" s="23" t="inlineStr">
         <is>
-          <t>妖精、不定形群</t>
+          <t>妖精群、不定形群</t>
         </is>
       </c>
       <c r="I424" s="23" t="n">
@@ -31124,7 +31124,7 @@
       </c>
       <c r="H425" s="23" t="inlineStr">
         <is>
-          <t>妖精、不定形群</t>
+          <t>妖精群、不定形群</t>
         </is>
       </c>
       <c r="I425" s="23" t="n">
@@ -31185,7 +31185,7 @@
       </c>
       <c r="H426" s="23" t="inlineStr">
         <is>
-          <t>妖精、不定形群</t>
+          <t>妖精群、不定形群</t>
         </is>
       </c>
       <c r="I426" s="23" t="n">
@@ -31246,7 +31246,7 @@
       </c>
       <c r="H427" s="23" t="inlineStr">
         <is>
-          <t>妖精、不定形群</t>
+          <t>妖精群、不定形群</t>
         </is>
       </c>
       <c r="I427" s="23" t="n">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="H433" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I433" s="23" t="n">
@@ -31852,7 +31852,7 @@
       </c>
       <c r="H437" s="23" t="inlineStr">
         <is>
-          <t>妖精、矿物群</t>
+          <t>妖精群、矿物群</t>
         </is>
       </c>
       <c r="I437" s="23" t="n">
@@ -31913,7 +31913,7 @@
       </c>
       <c r="H438" s="23" t="inlineStr">
         <is>
-          <t>妖精、矿物群</t>
+          <t>妖精群、矿物群</t>
         </is>
       </c>
       <c r="I438" s="23" t="n">
@@ -31974,7 +31974,7 @@
       </c>
       <c r="H439" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I439" s="23" t="n">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="H440" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I440" s="23" t="n">
@@ -32096,7 +32096,7 @@
       </c>
       <c r="H441" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I441" s="23" t="n">
@@ -32340,7 +32340,7 @@
       </c>
       <c r="H445" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中2群</t>
+          <t>水中1群、水中2群</t>
         </is>
       </c>
       <c r="I445" s="23" t="n">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="H466" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I466" s="23" t="n">
@@ -33630,7 +33630,7 @@
       </c>
       <c r="H467" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I467" s="23" t="n">
@@ -33691,7 +33691,7 @@
       </c>
       <c r="H468" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I468" s="23" t="n">
@@ -33752,7 +33752,7 @@
       </c>
       <c r="H469" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I469" s="23" t="n">
@@ -33813,7 +33813,7 @@
       </c>
       <c r="H470" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I470" s="23" t="n">
@@ -33874,7 +33874,7 @@
       </c>
       <c r="H471" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I471" s="23" t="n">
@@ -33935,7 +33935,7 @@
       </c>
       <c r="H472" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I472" s="23" t="n">
@@ -33996,7 +33996,7 @@
       </c>
       <c r="H473" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I473" s="23" t="n">
@@ -34057,7 +34057,7 @@
       </c>
       <c r="H474" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I474" s="23" t="n">
@@ -34301,7 +34301,7 @@
       </c>
       <c r="H478" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I478" s="23" t="n">
@@ -34362,7 +34362,7 @@
       </c>
       <c r="H479" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I479" s="23" t="n">
@@ -34785,7 +34785,7 @@
       </c>
       <c r="H486" s="23" t="inlineStr">
         <is>
-          <t>妖精、植物群</t>
+          <t>妖精群、植物群</t>
         </is>
       </c>
       <c r="I486" s="23" t="n">
@@ -35639,7 +35639,7 @@
       </c>
       <c r="H500" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I500" s="23" t="n">
@@ -35700,7 +35700,7 @@
       </c>
       <c r="H501" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I501" s="23" t="n">
@@ -35761,7 +35761,7 @@
       </c>
       <c r="H502" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I502" s="23" t="n">
@@ -35822,7 +35822,7 @@
       </c>
       <c r="H503" s="23" t="inlineStr">
         <is>
-          <t>妖精、植物群</t>
+          <t>妖精群、植物群</t>
         </is>
       </c>
       <c r="I503" s="23" t="n">
@@ -35883,7 +35883,7 @@
       </c>
       <c r="H504" s="23" t="inlineStr">
         <is>
-          <t>妖精、植物群</t>
+          <t>妖精群、植物群</t>
         </is>
       </c>
       <c r="I504" s="23" t="n">
@@ -35944,7 +35944,7 @@
       </c>
       <c r="H505" s="23" t="inlineStr">
         <is>
-          <t>妖精、植物群</t>
+          <t>妖精群、植物群</t>
         </is>
       </c>
       <c r="I505" s="23" t="n">
@@ -36005,7 +36005,7 @@
       </c>
       <c r="H506" s="23" t="inlineStr">
         <is>
-          <t>水中1、不定形群</t>
+          <t>水中1群、不定形群</t>
         </is>
       </c>
       <c r="I506" s="23" t="n">
@@ -36066,7 +36066,7 @@
       </c>
       <c r="H507" s="23" t="inlineStr">
         <is>
-          <t>水中1、不定形群</t>
+          <t>水中1群、不定形群</t>
         </is>
       </c>
       <c r="I507" s="23" t="n">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="H508" s="23" t="inlineStr">
         <is>
-          <t>水中1、不定形群</t>
+          <t>水中1群、不定形群</t>
         </is>
       </c>
       <c r="I508" s="23" t="n">
@@ -36188,7 +36188,7 @@
       </c>
       <c r="H509" s="23" t="inlineStr">
         <is>
-          <t>水中1、不定形群</t>
+          <t>水中1群、不定形群</t>
         </is>
       </c>
       <c r="I509" s="23" t="n">
@@ -36432,7 +36432,7 @@
       </c>
       <c r="H513" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I513" s="23" t="n">
@@ -36493,7 +36493,7 @@
       </c>
       <c r="H514" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I514" s="23" t="n">
@@ -37392,7 +37392,7 @@
       </c>
       <c r="H529" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I529" s="23" t="n">
@@ -37453,7 +37453,7 @@
       </c>
       <c r="H530" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I530" s="23" t="n">
@@ -37514,7 +37514,7 @@
       </c>
       <c r="H531" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I531" s="23" t="n">
@@ -37689,7 +37689,7 @@
       </c>
       <c r="H534" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I534" s="23" t="n">
@@ -37872,7 +37872,7 @@
       </c>
       <c r="H537" s="23" t="inlineStr">
         <is>
-          <t>虫、水中3群</t>
+          <t>虫群、水中3群</t>
         </is>
       </c>
       <c r="I537" s="23" t="n">
@@ -37933,7 +37933,7 @@
       </c>
       <c r="H538" s="23" t="inlineStr">
         <is>
-          <t>虫、水中3群</t>
+          <t>虫群、水中3群</t>
         </is>
       </c>
       <c r="I538" s="23" t="n">
@@ -38356,7 +38356,7 @@
       </c>
       <c r="H545" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I545" s="23" t="n">
@@ -38417,7 +38417,7 @@
       </c>
       <c r="H546" s="23" t="inlineStr">
         <is>
-          <t>怪兽、植物群</t>
+          <t>怪兽群、植物群</t>
         </is>
       </c>
       <c r="I546" s="23" t="n">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="H550" s="23" t="inlineStr">
         <is>
-          <t>怪兽、陆上群</t>
+          <t>怪兽群、陆上群</t>
         </is>
       </c>
       <c r="I550" s="23" t="n">
@@ -38905,7 +38905,7 @@
       </c>
       <c r="H554" s="23" t="inlineStr">
         <is>
-          <t>飞行、妖精群</t>
+          <t>飞行群、妖精群</t>
         </is>
       </c>
       <c r="I554" s="23" t="n">
@@ -39332,7 +39332,7 @@
       </c>
       <c r="H561" s="23" t="inlineStr">
         <is>
-          <t>人型、不定形群</t>
+          <t>人型群、不定形群</t>
         </is>
       </c>
       <c r="I561" s="23" t="n">
@@ -39515,7 +39515,7 @@
       </c>
       <c r="H564" s="23" t="inlineStr">
         <is>
-          <t>妖精、矿物群</t>
+          <t>妖精群、矿物群</t>
         </is>
       </c>
       <c r="I564" s="23" t="n">
@@ -40569,7 +40569,7 @@
       </c>
       <c r="H582" s="485" t="inlineStr">
         <is>
-          <t>水中1、妖精群</t>
+          <t>水中1群、妖精群</t>
         </is>
       </c>
       <c r="I582" s="485" t="n">
@@ -41884,7 +41884,7 @@
       </c>
       <c r="H605" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I605" s="23" t="n">
@@ -41945,7 +41945,7 @@
       </c>
       <c r="H606" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I606" s="23" t="n">
@@ -42006,7 +42006,7 @@
       </c>
       <c r="H607" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I607" s="23" t="n">
@@ -43897,7 +43897,7 @@
       </c>
       <c r="H638" s="23" t="inlineStr">
         <is>
-          <t>陆上、飞行群</t>
+          <t>陆上群、飞行群</t>
         </is>
       </c>
       <c r="I638" s="23" t="n">
@@ -43958,7 +43958,7 @@
       </c>
       <c r="H639" s="23" t="inlineStr">
         <is>
-          <t>陆上、飞行群</t>
+          <t>陆上群、飞行群</t>
         </is>
       </c>
       <c r="I639" s="23" t="n">
@@ -45056,7 +45056,7 @@
       </c>
       <c r="H657" s="23" t="inlineStr">
         <is>
-          <t>植物、妖精群</t>
+          <t>植物群、妖精群</t>
         </is>
       </c>
       <c r="I657" s="23" t="n">
@@ -45117,7 +45117,7 @@
       </c>
       <c r="H658" s="23" t="inlineStr">
         <is>
-          <t>植物、妖精群</t>
+          <t>植物群、妖精群</t>
         </is>
       </c>
       <c r="I658" s="23" t="n">
@@ -46154,7 +46154,7 @@
       </c>
       <c r="H675" s="23" t="inlineStr">
         <is>
-          <t>虫、矿物群</t>
+          <t>虫群、矿物群</t>
         </is>
       </c>
       <c r="I675" s="23" t="n">
@@ -46215,7 +46215,7 @@
       </c>
       <c r="H676" s="23" t="inlineStr">
         <is>
-          <t>虫、矿物群</t>
+          <t>虫群、矿物群</t>
         </is>
       </c>
       <c r="I676" s="23" t="n">
@@ -46276,7 +46276,7 @@
       </c>
       <c r="H677" s="23" t="inlineStr">
         <is>
-          <t>陆上、龙群</t>
+          <t>陆上群、龙群</t>
         </is>
       </c>
       <c r="I677" s="23" t="n">
@@ -46337,7 +46337,7 @@
       </c>
       <c r="H678" s="23" t="inlineStr">
         <is>
-          <t>陆上、龙群</t>
+          <t>陆上群、龙群</t>
         </is>
       </c>
       <c r="I678" s="23" t="n">
@@ -46459,7 +46459,7 @@
       </c>
       <c r="H680" s="23" t="inlineStr">
         <is>
-          <t>矿物、不定形群</t>
+          <t>矿物群、不定形群</t>
         </is>
       </c>
       <c r="I680" s="23" t="n">
@@ -46520,7 +46520,7 @@
       </c>
       <c r="H681" s="23" t="inlineStr">
         <is>
-          <t>矿物、不定形群</t>
+          <t>矿物群、不定形群</t>
         </is>
       </c>
       <c r="I681" s="23" t="n">
@@ -46581,7 +46581,7 @@
       </c>
       <c r="H682" s="23" t="inlineStr">
         <is>
-          <t>矿物、不定形群</t>
+          <t>矿物群、不定形群</t>
         </is>
       </c>
       <c r="I682" s="23" t="n">
@@ -46642,7 +46642,7 @@
       </c>
       <c r="H683" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I683" s="23" t="n">
@@ -46703,7 +46703,7 @@
       </c>
       <c r="H684" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I684" s="23" t="n">
@@ -46764,7 +46764,7 @@
       </c>
       <c r="H685" s="23" t="inlineStr">
         <is>
-          <t>飞行、水中3群</t>
+          <t>飞行群、水中3群</t>
         </is>
       </c>
       <c r="I685" s="23" t="n">
@@ -46825,7 +46825,7 @@
       </c>
       <c r="H686" s="23" t="inlineStr">
         <is>
-          <t>飞行、水中3群</t>
+          <t>飞行群、水中3群</t>
         </is>
       </c>
       <c r="I686" s="23" t="n">
@@ -47740,7 +47740,7 @@
       </c>
       <c r="H701" s="23" t="inlineStr">
         <is>
-          <t>水中1、飞行群</t>
+          <t>水中1群、飞行群</t>
         </is>
       </c>
       <c r="I701" s="23" t="n">
@@ -47801,7 +47801,7 @@
       </c>
       <c r="H702" s="23" t="inlineStr">
         <is>
-          <t>水中1、飞行群</t>
+          <t>水中1群、飞行群</t>
         </is>
       </c>
       <c r="I702" s="23" t="n">
@@ -48960,7 +48960,7 @@
       </c>
       <c r="H721" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中2群</t>
+          <t>水中1群、水中2群</t>
         </is>
       </c>
       <c r="I721" s="23" t="n">
@@ -49143,7 +49143,7 @@
       </c>
       <c r="H724" s="23" t="inlineStr">
         <is>
-          <t>植物、矿物群</t>
+          <t>植物群、矿物群</t>
         </is>
       </c>
       <c r="I724" s="23" t="n">
@@ -49204,7 +49204,7 @@
       </c>
       <c r="H725" s="23" t="inlineStr">
         <is>
-          <t>植物、矿物群</t>
+          <t>植物群、矿物群</t>
         </is>
       </c>
       <c r="I725" s="23" t="n">
@@ -49936,7 +49936,7 @@
       </c>
       <c r="H737" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I737" s="23" t="n">
@@ -49997,7 +49997,7 @@
       </c>
       <c r="H738" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I738" s="23" t="n">
@@ -50058,7 +50058,7 @@
       </c>
       <c r="H739" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I739" s="23" t="n">
@@ -50424,7 +50424,7 @@
       </c>
       <c r="H745" s="23" t="inlineStr">
         <is>
-          <t>水中1、不定形群</t>
+          <t>水中1群、不定形群</t>
         </is>
       </c>
       <c r="I745" s="23" t="n">
@@ -50485,7 +50485,7 @@
       </c>
       <c r="H746" s="23" t="inlineStr">
         <is>
-          <t>水中1、不定形群</t>
+          <t>水中1群、不定形群</t>
         </is>
       </c>
       <c r="I746" s="23" t="n">
@@ -50546,7 +50546,7 @@
       </c>
       <c r="H747" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I747" s="23" t="n">
@@ -50607,7 +50607,7 @@
       </c>
       <c r="H748" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I748" s="23" t="n">
@@ -50668,7 +50668,7 @@
       </c>
       <c r="H749" s="23" t="inlineStr">
         <is>
-          <t>龙、怪兽群</t>
+          <t>龙群、怪兽群</t>
         </is>
       </c>
       <c r="I749" s="23" t="n">
@@ -56265,7 +56265,7 @@
       </c>
       <c r="H842" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I842" s="23" t="n">
@@ -56326,7 +56326,7 @@
       </c>
       <c r="H843" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I843" s="23" t="n">
@@ -57607,7 +57607,7 @@
       </c>
       <c r="H864" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中2群</t>
+          <t>水中1群、水中2群</t>
         </is>
       </c>
       <c r="I864" s="23" t="n">
@@ -57668,7 +57668,7 @@
       </c>
       <c r="H865" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中2群</t>
+          <t>水中1群、水中2群</t>
         </is>
       </c>
       <c r="I865" s="23" t="n">
@@ -57851,7 +57851,7 @@
       </c>
       <c r="H868" s="23" t="inlineStr">
         <is>
-          <t>水中1、龙群</t>
+          <t>水中1群、龙群</t>
         </is>
       </c>
       <c r="I868" s="23" t="n">
@@ -57912,7 +57912,7 @@
       </c>
       <c r="H869" s="23" t="inlineStr">
         <is>
-          <t>水中1、龙群</t>
+          <t>水中1群、龙群</t>
         </is>
       </c>
       <c r="I869" s="23" t="n">
@@ -57973,7 +57973,7 @@
       </c>
       <c r="H870" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I870" s="23" t="n">
@@ -58034,7 +58034,7 @@
       </c>
       <c r="H871" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I871" s="23" t="n">
@@ -58095,7 +58095,7 @@
       </c>
       <c r="H872" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I872" s="23" t="n">
@@ -58156,7 +58156,7 @@
       </c>
       <c r="H873" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I873" s="23" t="n">
@@ -58217,7 +58217,7 @@
       </c>
       <c r="H874" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I874" s="23" t="n">
@@ -58278,7 +58278,7 @@
       </c>
       <c r="H875" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I875" s="23" t="n">
@@ -58522,7 +58522,7 @@
       </c>
       <c r="H879" s="23" t="inlineStr">
         <is>
-          <t>飞行、人型群</t>
+          <t>飞行群、人型群</t>
         </is>
       </c>
       <c r="I879" s="23" t="n">
@@ -58583,7 +58583,7 @@
       </c>
       <c r="H880" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I880" s="23" t="n">
@@ -58644,7 +58644,7 @@
       </c>
       <c r="H881" s="23" t="inlineStr">
         <is>
-          <t>妖精、矿物群</t>
+          <t>妖精群、矿物群</t>
         </is>
       </c>
       <c r="I881" s="23" t="n">
@@ -59071,7 +59071,7 @@
       </c>
       <c r="H888" s="23" t="inlineStr">
         <is>
-          <t>植物、不定形群</t>
+          <t>植物群、不定形群</t>
         </is>
       </c>
       <c r="I888" s="23" t="n">
@@ -59132,7 +59132,7 @@
       </c>
       <c r="H889" s="23" t="inlineStr">
         <is>
-          <t>植物、不定形群</t>
+          <t>植物群、不定形群</t>
         </is>
       </c>
       <c r="I889" s="23" t="n">
@@ -59315,7 +59315,7 @@
       </c>
       <c r="H892" s="23" t="inlineStr">
         <is>
-          <t>怪兽、矿物群</t>
+          <t>怪兽群、矿物群</t>
         </is>
       </c>
       <c r="I892" s="23" t="n">
@@ -59376,7 +59376,7 @@
       </c>
       <c r="H893" s="23" t="inlineStr">
         <is>
-          <t>怪兽、矿物群</t>
+          <t>怪兽群、矿物群</t>
         </is>
       </c>
       <c r="I893" s="23" t="n">
@@ -59437,7 +59437,7 @@
       </c>
       <c r="H894" s="23" t="inlineStr">
         <is>
-          <t>怪兽、矿物群</t>
+          <t>怪兽群、矿物群</t>
         </is>
       </c>
       <c r="I894" s="23" t="n">
@@ -59498,7 +59498,7 @@
       </c>
       <c r="H895" s="23" t="inlineStr">
         <is>
-          <t>飞行、龙群</t>
+          <t>飞行群、龙群</t>
         </is>
       </c>
       <c r="I895" s="23" t="n">
@@ -59559,7 +59559,7 @@
       </c>
       <c r="H896" s="23" t="inlineStr">
         <is>
-          <t>飞行、龙群</t>
+          <t>飞行群、龙群</t>
         </is>
       </c>
       <c r="I896" s="23" t="n">
@@ -60442,7 +60442,7 @@
       </c>
       <c r="H911" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I911" s="23" t="n">
@@ -60503,7 +60503,7 @@
       </c>
       <c r="H912" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I912" s="23" t="n">
@@ -60564,7 +60564,7 @@
       </c>
       <c r="H913" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I913" s="23" t="n">
@@ -61296,7 +61296,7 @@
       </c>
       <c r="H925" s="23" t="inlineStr">
         <is>
-          <t>虫、妖精群</t>
+          <t>虫群、妖精群</t>
         </is>
       </c>
       <c r="I925" s="23" t="n">
@@ -61357,7 +61357,7 @@
       </c>
       <c r="H926" s="23" t="inlineStr">
         <is>
-          <t>虫、妖精群</t>
+          <t>虫群、妖精群</t>
         </is>
       </c>
       <c r="I926" s="23" t="n">
@@ -61845,7 +61845,7 @@
       </c>
       <c r="H934" s="23" t="inlineStr">
         <is>
-          <t>水中1、虫群</t>
+          <t>水中1群、虫群</t>
         </is>
       </c>
       <c r="I934" s="23" t="n">
@@ -61906,7 +61906,7 @@
       </c>
       <c r="H935" s="23" t="inlineStr">
         <is>
-          <t>水中1、虫群</t>
+          <t>水中1群、虫群</t>
         </is>
       </c>
       <c r="I935" s="23" t="n">
@@ -62211,7 +62211,7 @@
       </c>
       <c r="H940" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I940" s="23" t="n">
@@ -62272,7 +62272,7 @@
       </c>
       <c r="H941" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I941" s="23" t="n">
@@ -62821,7 +62821,7 @@
       </c>
       <c r="H950" s="23" t="inlineStr">
         <is>
-          <t>虫、水中3群</t>
+          <t>虫群、水中3群</t>
         </is>
       </c>
       <c r="I950" s="23" t="n">
@@ -62882,7 +62882,7 @@
       </c>
       <c r="H951" s="23" t="inlineStr">
         <is>
-          <t>虫、水中3群</t>
+          <t>虫群、水中3群</t>
         </is>
       </c>
       <c r="I951" s="23" t="n">
@@ -63362,7 +63362,7 @@
       </c>
       <c r="H959" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I959" s="23" t="n">
@@ -63423,7 +63423,7 @@
       </c>
       <c r="H960" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I960" s="23" t="n">
@@ -63606,7 +63606,7 @@
       </c>
       <c r="H963" s="23" t="inlineStr">
         <is>
-          <t>怪兽、龙群</t>
+          <t>怪兽群、龙群</t>
         </is>
       </c>
       <c r="I963" s="23" t="n">
@@ -65336,7 +65336,7 @@
       </c>
       <c r="H993" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I993" s="23" t="n">
@@ -65397,7 +65397,7 @@
       </c>
       <c r="H994" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I994" s="23" t="n">
@@ -65458,7 +65458,7 @@
       </c>
       <c r="H995" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I995" s="23" t="n">
@@ -65519,7 +65519,7 @@
       </c>
       <c r="H996" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I996" s="23" t="n">
@@ -65580,7 +65580,7 @@
       </c>
       <c r="H997" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I997" s="23" t="n">
@@ -65641,7 +65641,7 @@
       </c>
       <c r="H998" s="23" t="inlineStr">
         <is>
-          <t>陆上、人型群</t>
+          <t>陆上群、人型群</t>
         </is>
       </c>
       <c r="I998" s="23" t="n">
@@ -65702,7 +65702,7 @@
       </c>
       <c r="H999" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I999" s="23" t="n">
@@ -65763,7 +65763,7 @@
       </c>
       <c r="H1000" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I1000" s="23" t="n">
@@ -65824,7 +65824,7 @@
       </c>
       <c r="H1001" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I1001" s="23" t="n">
@@ -66739,7 +66739,7 @@
       </c>
       <c r="H1016" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I1016" s="23" t="n">
@@ -66800,7 +66800,7 @@
       </c>
       <c r="H1017" s="23" t="inlineStr">
         <is>
-          <t>怪兽、水中1群</t>
+          <t>怪兽群、水中1群</t>
         </is>
       </c>
       <c r="I1017" s="23" t="n">
@@ -67166,7 +67166,7 @@
       </c>
       <c r="H1023" s="23" t="inlineStr">
         <is>
-          <t>植物、龙群</t>
+          <t>植物群、龙群</t>
         </is>
       </c>
       <c r="I1023" s="23" t="n">
@@ -67227,7 +67227,7 @@
       </c>
       <c r="H1024" s="23" t="inlineStr">
         <is>
-          <t>植物、龙群</t>
+          <t>植物群、龙群</t>
         </is>
       </c>
       <c r="I1024" s="23" t="n">
@@ -67288,7 +67288,7 @@
       </c>
       <c r="H1025" s="23" t="inlineStr">
         <is>
-          <t>植物、龙群</t>
+          <t>植物群、龙群</t>
         </is>
       </c>
       <c r="I1025" s="23" t="n">
@@ -67349,7 +67349,7 @@
       </c>
       <c r="H1026" s="23" t="inlineStr">
         <is>
-          <t>陆上、龙群</t>
+          <t>陆上群、龙群</t>
         </is>
       </c>
       <c r="I1026" s="23" t="n">
@@ -67410,7 +67410,7 @@
       </c>
       <c r="H1027" s="23" t="inlineStr">
         <is>
-          <t>陆上、龙群</t>
+          <t>陆上群、龙群</t>
         </is>
       </c>
       <c r="I1027" s="23" t="n">
@@ -67471,7 +67471,7 @@
       </c>
       <c r="H1028" s="23" t="inlineStr">
         <is>
-          <t>水中1、飞行群</t>
+          <t>水中1群、飞行群</t>
         </is>
       </c>
       <c r="I1028" s="23" t="n">
@@ -67894,7 +67894,7 @@
       </c>
       <c r="H1035" s="23" t="inlineStr">
         <is>
-          <t>水中1、人型群</t>
+          <t>水中1群、人型群</t>
         </is>
       </c>
       <c r="I1035" s="23" t="n">
@@ -67955,7 +67955,7 @@
       </c>
       <c r="H1036" s="23" t="inlineStr">
         <is>
-          <t>水中1、人型群</t>
+          <t>水中1群、人型群</t>
         </is>
       </c>
       <c r="I1036" s="23" t="n">
@@ -68016,7 +68016,7 @@
       </c>
       <c r="H1037" s="23" t="inlineStr">
         <is>
-          <t>矿物、不定形群</t>
+          <t>矿物群、不定形群</t>
         </is>
       </c>
       <c r="I1037" s="23" t="n">
@@ -68077,7 +68077,7 @@
       </c>
       <c r="H1038" s="23" t="inlineStr">
         <is>
-          <t>矿物、不定形群</t>
+          <t>矿物群、不定形群</t>
         </is>
       </c>
       <c r="I1038" s="23" t="n">
@@ -68321,7 +68321,7 @@
       </c>
       <c r="H1042" s="23" t="inlineStr">
         <is>
-          <t>妖精、人型群</t>
+          <t>妖精群、人型群</t>
         </is>
       </c>
       <c r="I1042" s="23" t="n">
@@ -68382,7 +68382,7 @@
       </c>
       <c r="H1043" s="23" t="inlineStr">
         <is>
-          <t>妖精、人型群</t>
+          <t>妖精群、人型群</t>
         </is>
       </c>
       <c r="I1043" s="23" t="n">
@@ -68443,7 +68443,7 @@
       </c>
       <c r="H1044" s="23" t="inlineStr">
         <is>
-          <t>妖精、人型群</t>
+          <t>妖精群、人型群</t>
         </is>
       </c>
       <c r="I1044" s="23" t="n">
@@ -68626,7 +68626,7 @@
       </c>
       <c r="H1047" s="23" t="inlineStr">
         <is>
-          <t>水中1、水中3群</t>
+          <t>水中1群、水中3群</t>
         </is>
       </c>
       <c r="I1047" s="23" t="n">
@@ -68687,7 +68687,7 @@
       </c>
       <c r="H1048" s="23" t="inlineStr">
         <is>
-          <t>飞行、陆上群</t>
+          <t>飞行群、陆上群</t>
         </is>
       </c>
       <c r="I1048" s="23" t="n">
@@ -68809,7 +68809,7 @@
       </c>
       <c r="H1050" s="23" t="inlineStr">
         <is>
-          <t>矿物、不定形群</t>
+          <t>矿物群、不定形群</t>
         </is>
       </c>
       <c r="I1050" s="23" t="n">
@@ -68870,7 +68870,7 @@
       </c>
       <c r="H1051" s="23" t="inlineStr">
         <is>
-          <t>妖精、不定形群</t>
+          <t>妖精群、不定形群</t>
         </is>
       </c>
       <c r="I1051" s="23" t="n">
@@ -68931,7 +68931,7 @@
       </c>
       <c r="H1052" s="23" t="inlineStr">
         <is>
-          <t>妖精、不定形群</t>
+          <t>妖精群、不定形群</t>
         </is>
       </c>
       <c r="I1052" s="23" t="n">
@@ -68992,7 +68992,7 @@
       </c>
       <c r="H1053" s="23" t="inlineStr">
         <is>
-          <t>妖精、矿物群</t>
+          <t>妖精群、矿物群</t>
         </is>
       </c>
       <c r="I1053" s="23" t="n">
@@ -69053,7 +69053,7 @@
       </c>
       <c r="H1054" s="23" t="inlineStr">
         <is>
-          <t>水中1、不定形群</t>
+          <t>水中1群、不定形群</t>
         </is>
       </c>
       <c r="I1054" s="23" t="n">
@@ -69297,7 +69297,7 @@
       </c>
       <c r="H1058" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I1058" s="23" t="n">
@@ -69419,7 +69419,7 @@
       </c>
       <c r="H1060" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I1060" s="23" t="n">
@@ -69480,7 +69480,7 @@
       </c>
       <c r="H1061" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I1061" s="23" t="n">
@@ -69541,7 +69541,7 @@
       </c>
       <c r="H1062" s="23" t="inlineStr">
         <is>
-          <t>陆上、矿物群</t>
+          <t>陆上群、矿物群</t>
         </is>
       </c>
       <c r="I1062" s="23" t="n">
@@ -69602,7 +69602,7 @@
       </c>
       <c r="H1063" s="23" t="inlineStr">
         <is>
-          <t>陆上、矿物群</t>
+          <t>陆上群、矿物群</t>
         </is>
       </c>
       <c r="I1063" s="23" t="n">
@@ -69891,7 +69891,7 @@
       </c>
       <c r="H1068" s="23" t="inlineStr">
         <is>
-          <t>矿物、龙群</t>
+          <t>矿物群、龙群</t>
         </is>
       </c>
       <c r="I1068" s="23" t="n">
@@ -69952,7 +69952,7 @@
       </c>
       <c r="H1069" s="23" t="inlineStr">
         <is>
-          <t>不定形、龙群</t>
+          <t>不定形群、龙群</t>
         </is>
       </c>
       <c r="I1069" s="23" t="n">
@@ -70013,7 +70013,7 @@
       </c>
       <c r="H1070" s="23" t="inlineStr">
         <is>
-          <t>不定形、龙群</t>
+          <t>不定形群、龙群</t>
         </is>
       </c>
       <c r="I1070" s="23" t="n">
@@ -70074,7 +70074,7 @@
       </c>
       <c r="H1071" s="23" t="inlineStr">
         <is>
-          <t>不定形、龙群</t>
+          <t>不定形群、龙群</t>
         </is>
       </c>
       <c r="I1071" s="23" t="n">
@@ -71299,7 +71299,7 @@
       </c>
       <c r="H1092" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I1092" s="23" t="n">
@@ -71360,7 +71360,7 @@
       </c>
       <c r="H1093" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I1093" s="23" t="n">
@@ -71421,7 +71421,7 @@
       </c>
       <c r="H1094" s="23" t="inlineStr">
         <is>
-          <t>陆上、植物群</t>
+          <t>陆上群、植物群</t>
         </is>
       </c>
       <c r="I1094" s="23" t="n">
@@ -71665,7 +71665,7 @@
       </c>
       <c r="H1098" s="23" t="inlineStr">
         <is>
-          <t>飞行、水中1群</t>
+          <t>飞行群、水中1群</t>
         </is>
       </c>
       <c r="I1098" s="23" t="n">
@@ -71726,7 +71726,7 @@
       </c>
       <c r="H1099" s="23" t="inlineStr">
         <is>
-          <t>飞行、水中1群</t>
+          <t>飞行群、水中1群</t>
         </is>
       </c>
       <c r="I1099" s="23" t="n">
@@ -71787,7 +71787,7 @@
       </c>
       <c r="H1100" s="23" t="inlineStr">
         <is>
-          <t>飞行、水中1群</t>
+          <t>飞行群、水中1群</t>
         </is>
       </c>
       <c r="I1100" s="23" t="n">
@@ -72397,7 +72397,7 @@
       </c>
       <c r="H1110" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I1110" s="23" t="n">
@@ -72458,7 +72458,7 @@
       </c>
       <c r="H1111" s="23" t="inlineStr">
         <is>
-          <t>陆上、妖精群</t>
+          <t>陆上群、妖精群</t>
         </is>
       </c>
       <c r="I1111" s="23" t="n">
@@ -72519,7 +72519,7 @@
       </c>
       <c r="H1112" s="23" t="inlineStr">
         <is>
-          <t>陆上、矿物群</t>
+          <t>陆上群、矿物群</t>
         </is>
       </c>
       <c r="I1112" s="23" t="n">
@@ -72580,7 +72580,7 @@
       </c>
       <c r="H1113" s="23" t="inlineStr">
         <is>
-          <t>陆上、矿物群</t>
+          <t>陆上群、矿物群</t>
         </is>
       </c>
       <c r="I1113" s="23" t="n">
@@ -73373,7 +73373,7 @@
       </c>
       <c r="H1126" s="23" t="inlineStr">
         <is>
-          <t>水中1、飞行群</t>
+          <t>水中1群、飞行群</t>
         </is>
       </c>
       <c r="I1126" s="23" t="n">
@@ -73434,7 +73434,7 @@
       </c>
       <c r="H1127" s="23" t="inlineStr">
         <is>
-          <t>水中1、飞行群</t>
+          <t>水中1群、飞行群</t>
         </is>
       </c>
       <c r="I1127" s="23" t="n">
@@ -74776,7 +74776,7 @@
       </c>
       <c r="H1149" s="23" t="inlineStr">
         <is>
-          <t>陆上、水中2群</t>
+          <t>陆上群、水中2群</t>
         </is>
       </c>
       <c r="I1149" s="23" t="n">
@@ -74837,7 +74837,7 @@
       </c>
       <c r="H1150" s="23" t="inlineStr">
         <is>
-          <t>陆上、水中2群</t>
+          <t>陆上群、水中2群</t>
         </is>
       </c>
       <c r="I1150" s="23" t="n">
@@ -75813,7 +75813,7 @@
       </c>
       <c r="H1166" s="23" t="inlineStr">
         <is>
-          <t>水中1、陆上群</t>
+          <t>水中1群、陆上群</t>
         </is>
       </c>
       <c r="I1166" s="23" t="n">
@@ -76741,7 +76741,7 @@
       </c>
       <c r="H1182" s="23" t="inlineStr">
         <is>
-          <t>龙、矿物群</t>
+          <t>龙群、矿物群</t>
         </is>
       </c>
       <c r="I1182" s="23" t="n">
@@ -76802,7 +76802,7 @@
       </c>
       <c r="H1183" s="23" t="inlineStr">
         <is>
-          <t>龙、矿物群</t>
+          <t>龙群、矿物群</t>
         </is>
       </c>
       <c r="I1183" s="23" t="n">
@@ -76863,7 +76863,7 @@
       </c>
       <c r="H1184" s="23" t="inlineStr">
         <is>
-          <t>龙、矿物群</t>
+          <t>龙群、矿物群</t>
         </is>
       </c>
       <c r="I1184" s="23" t="n">
@@ -77608,7 +77608,7 @@
       </c>
       <c r="H1197" s="23" t="inlineStr">
         <is>
-          <t>植物、龙群</t>
+          <t>植物群、龙群</t>
         </is>
       </c>
       <c r="I1197" s="23" t="n">
@@ -77669,7 +77669,7 @@
       </c>
       <c r="H1198" s="23" t="inlineStr">
         <is>
-          <t>矿物、不定形群</t>
+          <t>矿物群、不定形群</t>
         </is>
       </c>
       <c r="I1198" s="23" t="n">
@@ -77730,7 +77730,7 @@
       </c>
       <c r="H1199" s="23" t="inlineStr">
         <is>
-          <t>矿物、不定形群</t>
+          <t>矿物群、不定形群</t>
         </is>
       </c>
       <c r="I1199" s="23" t="n">
@@ -78019,7 +78019,7 @@
       </c>
       <c r="H1204" s="23" t="inlineStr">
         <is>
-          <t>矿物、龙群</t>
+          <t>矿物群、龙群</t>
         </is>
       </c>
       <c r="I1204" s="23" t="n">
@@ -78080,7 +78080,7 @@
       </c>
       <c r="H1205" s="23" t="inlineStr">
         <is>
-          <t>植物、龙群</t>
+          <t>植物群、龙群</t>
         </is>
       </c>
       <c r="I1205" s="23" t="n">
@@ -78196,11 +78196,7 @@
           <t>无性别</t>
         </is>
       </c>
-      <c r="H1207" s="485" t="inlineStr">
-        <is>
-          <t>未知蛋群</t>
-        </is>
-      </c>
+      <c r="H1207" s="485" t="inlineStr"/>
       <c r="I1207" s="485" t="n">
         <v>125</v>
       </c>

--- a/docs/宝可梦图鉴.xlsx
+++ b/docs/宝可梦图鉴.xlsx
@@ -214,7 +214,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="282">
+  <fills count="287">
     <fill>
       <patternFill/>
     </fill>
@@ -2627,6 +2627,56 @@
         <fgColor rgb="FFA98FF3"/>
       </patternFill>
     </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFF7D02C"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFF95587"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FF96D9D6"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFB7B7CE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FF96D9D6"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFD685AD"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFA8A77A"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FF735797"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FF96D9D6"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFB6A136"/>
+        </stop>
+      </gradientFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -2897,7 +2947,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="714">
+  <cellXfs count="722">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4996,6 +5046,30 @@
     <xf numFmtId="0" fontId="25" fillId="99" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="282" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="283" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="284" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="204" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="205" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="140" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="285" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="286" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6730,9 +6804,9 @@
           <t>小拉达-阿罗拉</t>
         </is>
       </c>
-      <c r="C22" s="457" t="inlineStr">
-        <is>
-          <t>一般</t>
+      <c r="C22" s="664" t="inlineStr">
+        <is>
+          <t>恶/一般</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -6852,9 +6926,9 @@
           <t>拉达-阿罗拉</t>
         </is>
       </c>
-      <c r="C24" s="457" t="inlineStr">
-        <is>
-          <t>一般</t>
+      <c r="C24" s="664" t="inlineStr">
+        <is>
+          <t>恶/一般</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -7279,9 +7353,9 @@
           <t>雷丘-阿罗拉</t>
         </is>
       </c>
-      <c r="C31" s="459" t="inlineStr">
-        <is>
-          <t>电</t>
+      <c r="C31" s="714" t="inlineStr">
+        <is>
+          <t>电/超能</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -7401,9 +7475,9 @@
           <t>穿山鼠-阿罗拉</t>
         </is>
       </c>
-      <c r="C33" s="460" t="inlineStr">
-        <is>
-          <t>地面</t>
+      <c r="C33" s="715" t="inlineStr">
+        <is>
+          <t>冰/钢</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -7523,9 +7597,9 @@
           <t>穿山王-阿罗拉</t>
         </is>
       </c>
-      <c r="C35" s="460" t="inlineStr">
-        <is>
-          <t>地面</t>
+      <c r="C35" s="715" t="inlineStr">
+        <is>
+          <t>冰/钢</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -8125,9 +8199,9 @@
           <t>六尾-阿罗拉</t>
         </is>
       </c>
-      <c r="C45" s="450" t="inlineStr">
-        <is>
-          <t>火</t>
+      <c r="C45" s="540" t="inlineStr">
+        <is>
+          <t>冰</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
@@ -8247,9 +8321,9 @@
           <t>九尾-阿罗拉</t>
         </is>
       </c>
-      <c r="C47" s="450" t="inlineStr">
-        <is>
-          <t>火</t>
+      <c r="C47" s="716" t="inlineStr">
+        <is>
+          <t>冰/妖精</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -9040,9 +9114,9 @@
           <t>地鼠-阿罗拉</t>
         </is>
       </c>
-      <c r="C60" s="460" t="inlineStr">
-        <is>
-          <t>地面</t>
+      <c r="C60" s="586" t="inlineStr">
+        <is>
+          <t>地面/钢</t>
         </is>
       </c>
       <c r="D60" s="23" t="inlineStr">
@@ -9162,9 +9236,9 @@
           <t>三地鼠-阿罗拉</t>
         </is>
       </c>
-      <c r="C62" s="460" t="inlineStr">
-        <is>
-          <t>地面</t>
+      <c r="C62" s="586" t="inlineStr">
+        <is>
+          <t>地面/钢</t>
         </is>
       </c>
       <c r="D62" s="23" t="inlineStr">
@@ -9284,9 +9358,9 @@
           <t>喵喵-伽勒尔</t>
         </is>
       </c>
-      <c r="C64" s="457" t="inlineStr">
-        <is>
-          <t>一般</t>
+      <c r="C64" s="596" t="inlineStr">
+        <is>
+          <t>钢</t>
         </is>
       </c>
       <c r="D64" s="23" t="inlineStr">
@@ -9345,9 +9419,9 @@
           <t>喵喵-阿罗拉</t>
         </is>
       </c>
-      <c r="C65" s="457" t="inlineStr">
-        <is>
-          <t>一般</t>
+      <c r="C65" s="499" t="inlineStr">
+        <is>
+          <t>恶</t>
         </is>
       </c>
       <c r="D65" s="23" t="inlineStr">
@@ -9467,9 +9541,9 @@
           <t>猫老大-阿罗拉</t>
         </is>
       </c>
-      <c r="C67" s="457" t="inlineStr">
-        <is>
-          <t>一般</t>
+      <c r="C67" s="499" t="inlineStr">
+        <is>
+          <t>恶</t>
         </is>
       </c>
       <c r="D67" s="23" t="inlineStr">
@@ -9833,9 +9907,9 @@
           <t>卡蒂狗-洗翠</t>
         </is>
       </c>
-      <c r="C73" s="450" t="inlineStr">
-        <is>
-          <t>火</t>
+      <c r="C73" s="509" t="inlineStr">
+        <is>
+          <t>火/岩石</t>
         </is>
       </c>
       <c r="D73" s="23" t="inlineStr">
@@ -9955,9 +10029,9 @@
           <t>风速狗-洗翠</t>
         </is>
       </c>
-      <c r="C75" s="450" t="inlineStr">
-        <is>
-          <t>火</t>
+      <c r="C75" s="509" t="inlineStr">
+        <is>
+          <t>火/岩石</t>
         </is>
       </c>
       <c r="D75" s="23" t="inlineStr">
@@ -10931,9 +11005,9 @@
           <t>小拳石-阿罗拉</t>
         </is>
       </c>
-      <c r="C91" s="470" t="inlineStr">
-        <is>
-          <t>岩石/地面</t>
+      <c r="C91" s="696" t="inlineStr">
+        <is>
+          <t>岩石/电</t>
         </is>
       </c>
       <c r="D91" s="23" t="inlineStr">
@@ -11053,9 +11127,9 @@
           <t>隆隆石-阿罗拉</t>
         </is>
       </c>
-      <c r="C93" s="470" t="inlineStr">
-        <is>
-          <t>岩石/地面</t>
+      <c r="C93" s="696" t="inlineStr">
+        <is>
+          <t>岩石/电</t>
         </is>
       </c>
       <c r="D93" s="23" t="inlineStr">
@@ -11175,9 +11249,9 @@
           <t>隆隆岩-阿罗拉</t>
         </is>
       </c>
-      <c r="C95" s="470" t="inlineStr">
-        <is>
-          <t>岩石/地面</t>
+      <c r="C95" s="696" t="inlineStr">
+        <is>
+          <t>岩石/电</t>
         </is>
       </c>
       <c r="D95" s="23" t="inlineStr">
@@ -11297,9 +11371,9 @@
           <t>小火马-伽勒尔</t>
         </is>
       </c>
-      <c r="C97" s="450" t="inlineStr">
-        <is>
-          <t>火</t>
+      <c r="C97" s="468" t="inlineStr">
+        <is>
+          <t>超能</t>
         </is>
       </c>
       <c r="D97" s="23" t="inlineStr">
@@ -11419,9 +11493,9 @@
           <t>烈焰马-伽勒尔</t>
         </is>
       </c>
-      <c r="C99" s="450" t="inlineStr">
-        <is>
-          <t>火</t>
+      <c r="C99" s="478" t="inlineStr">
+        <is>
+          <t>超能/妖精</t>
         </is>
       </c>
       <c r="D99" s="23" t="inlineStr">
@@ -11541,9 +11615,9 @@
           <t>呆呆兽-伽勒尔</t>
         </is>
       </c>
-      <c r="C101" s="471" t="inlineStr">
-        <is>
-          <t>水/超能</t>
+      <c r="C101" s="468" t="inlineStr">
+        <is>
+          <t>超能</t>
         </is>
       </c>
       <c r="D101" s="23" t="inlineStr">
@@ -11663,9 +11737,9 @@
           <t>呆壳兽-伽勒尔</t>
         </is>
       </c>
-      <c r="C103" s="471" t="inlineStr">
-        <is>
-          <t>水/超能</t>
+      <c r="C103" s="717" t="inlineStr">
+        <is>
+          <t>毒/超能</t>
         </is>
       </c>
       <c r="D103" s="23" t="inlineStr">
@@ -11907,9 +11981,9 @@
           <t>大葱鸭-伽勒尔</t>
         </is>
       </c>
-      <c r="C107" s="456" t="inlineStr">
-        <is>
-          <t>一般/飞行</t>
+      <c r="C107" s="466" t="inlineStr">
+        <is>
+          <t>格斗</t>
         </is>
       </c>
       <c r="D107" s="23" t="inlineStr">
@@ -12273,9 +12347,9 @@
           <t>臭泥-阿罗拉</t>
         </is>
       </c>
-      <c r="C113" s="458" t="inlineStr">
-        <is>
-          <t>毒</t>
+      <c r="C113" s="556" t="inlineStr">
+        <is>
+          <t>毒/恶</t>
         </is>
       </c>
       <c r="D113" s="23" t="inlineStr">
@@ -12395,9 +12469,9 @@
           <t>臭臭泥-阿罗拉</t>
         </is>
       </c>
-      <c r="C115" s="458" t="inlineStr">
-        <is>
-          <t>毒</t>
+      <c r="C115" s="556" t="inlineStr">
+        <is>
+          <t>毒/恶</t>
         </is>
       </c>
       <c r="D115" s="23" t="inlineStr">
@@ -13127,9 +13201,9 @@
           <t>霹雳电球-洗翠</t>
         </is>
       </c>
-      <c r="C127" s="459" t="inlineStr">
-        <is>
-          <t>电</t>
+      <c r="C127" s="566" t="inlineStr">
+        <is>
+          <t>电/草</t>
         </is>
       </c>
       <c r="D127" s="23" t="inlineStr">
@@ -13249,9 +13323,9 @@
           <t>顽皮雷弹-洗翠</t>
         </is>
       </c>
-      <c r="C129" s="459" t="inlineStr">
-        <is>
-          <t>电</t>
+      <c r="C129" s="566" t="inlineStr">
+        <is>
+          <t>电/草</t>
         </is>
       </c>
       <c r="D129" s="23" t="inlineStr">
@@ -13432,9 +13506,9 @@
           <t>椰蛋树-阿罗拉</t>
         </is>
       </c>
-      <c r="C132" s="475" t="inlineStr">
-        <is>
-          <t>草/超能</t>
+      <c r="C132" s="659" t="inlineStr">
+        <is>
+          <t>草/龙</t>
         </is>
       </c>
       <c r="D132" s="23" t="inlineStr">
@@ -13615,9 +13689,9 @@
           <t>嘎啦嘎啦-阿罗拉</t>
         </is>
       </c>
-      <c r="C135" s="460" t="inlineStr">
-        <is>
-          <t>地面</t>
+      <c r="C135" s="654" t="inlineStr">
+        <is>
+          <t>火/幽灵</t>
         </is>
       </c>
       <c r="D135" s="23" t="inlineStr">
@@ -13981,9 +14055,9 @@
           <t>双弹瓦斯-伽勒尔</t>
         </is>
       </c>
-      <c r="C141" s="458" t="inlineStr">
-        <is>
-          <t>毒</t>
+      <c r="C141" s="718" t="inlineStr">
+        <is>
+          <t>毒/妖精</t>
         </is>
       </c>
       <c r="D141" s="23" t="inlineStr">
@@ -14774,9 +14848,9 @@
           <t>魔墙人偶-伽勒尔</t>
         </is>
       </c>
-      <c r="C154" s="478" t="inlineStr">
-        <is>
-          <t>超能/妖精</t>
+      <c r="C154" s="479" t="inlineStr">
+        <is>
+          <t>冰/超能</t>
         </is>
       </c>
       <c r="D154" s="23" t="inlineStr">
@@ -15231,19 +15305,19 @@
         <v>75</v>
       </c>
       <c r="J161" s="23" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="K161" s="23" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L161" s="23" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M161" s="23" t="n">
         <v>70</v>
       </c>
       <c r="N161" s="23" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O161" s="23" t="inlineStr">
         <is>
@@ -15292,19 +15366,19 @@
         <v>75</v>
       </c>
       <c r="J162" s="23" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="K162" s="23" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L162" s="23" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M162" s="23" t="n">
         <v>70</v>
       </c>
       <c r="N162" s="23" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O162" s="23" t="inlineStr">
         <is>
@@ -15353,19 +15427,19 @@
         <v>75</v>
       </c>
       <c r="J163" s="23" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="K163" s="23" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L163" s="23" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M163" s="23" t="n">
         <v>70</v>
       </c>
       <c r="N163" s="23" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O163" s="23" t="inlineStr">
         <is>
@@ -16356,9 +16430,9 @@
           <t>急冻鸟-伽勒尔</t>
         </is>
       </c>
-      <c r="C180" s="486" t="inlineStr">
-        <is>
-          <t>冰/飞行</t>
+      <c r="C180" s="520" t="inlineStr">
+        <is>
+          <t>超能/飞行</t>
         </is>
       </c>
       <c r="D180" s="485" t="inlineStr">
@@ -16470,9 +16544,9 @@
           <t>闪电鸟-伽勒尔</t>
         </is>
       </c>
-      <c r="C182" s="487" t="inlineStr">
-        <is>
-          <t>电/飞行</t>
+      <c r="C182" s="719" t="inlineStr">
+        <is>
+          <t>格斗/飞行</t>
         </is>
       </c>
       <c r="D182" s="485" t="inlineStr">
@@ -16584,9 +16658,9 @@
           <t>火焰鸟-伽勒尔</t>
         </is>
       </c>
-      <c r="C184" s="488" t="inlineStr">
-        <is>
-          <t>火/飞行</t>
+      <c r="C184" s="629" t="inlineStr">
+        <is>
+          <t>恶/飞行</t>
         </is>
       </c>
       <c r="D184" s="485" t="inlineStr">
@@ -17304,9 +17378,9 @@
           <t>火暴兽-洗翠</t>
         </is>
       </c>
-      <c r="C196" s="450" t="inlineStr">
-        <is>
-          <t>火</t>
+      <c r="C196" s="654" t="inlineStr">
+        <is>
+          <t>火/幽灵</t>
         </is>
       </c>
       <c r="D196" s="23" t="inlineStr">
@@ -19606,9 +19680,9 @@
           <t>乌波-帕底亚</t>
         </is>
       </c>
-      <c r="C234" s="498" t="inlineStr">
-        <is>
-          <t>水/地面</t>
+      <c r="C234" s="461" t="inlineStr">
+        <is>
+          <t>毒/地面</t>
         </is>
       </c>
       <c r="D234" s="23" t="inlineStr">
@@ -19972,9 +20046,9 @@
           <t>呆呆王-伽勒尔</t>
         </is>
       </c>
-      <c r="C240" s="471" t="inlineStr">
-        <is>
-          <t>水/超能</t>
+      <c r="C240" s="717" t="inlineStr">
+        <is>
+          <t>毒/超能</t>
         </is>
       </c>
       <c r="D240" s="23" t="inlineStr">
@@ -22300,9 +22374,9 @@
           <t>千针鱼-洗翠</t>
         </is>
       </c>
-      <c r="C280" s="469" t="inlineStr">
-        <is>
-          <t>水/毒</t>
+      <c r="C280" s="676" t="inlineStr">
+        <is>
+          <t>恶/毒</t>
         </is>
       </c>
       <c r="D280" s="23" t="inlineStr">
@@ -22605,9 +22679,9 @@
           <t>狃拉-洗翠</t>
         </is>
       </c>
-      <c r="C285" s="508" t="inlineStr">
-        <is>
-          <t>恶/冰</t>
+      <c r="C285" s="675" t="inlineStr">
+        <is>
+          <t>格斗/毒</t>
         </is>
       </c>
       <c r="D285" s="23" t="inlineStr">
@@ -23093,9 +23167,9 @@
           <t>太阳珊瑚-伽勒尔</t>
         </is>
       </c>
-      <c r="C293" s="511" t="inlineStr">
-        <is>
-          <t>水/岩石</t>
+      <c r="C293" s="501" t="inlineStr">
+        <is>
+          <t>幽灵</t>
         </is>
       </c>
       <c r="D293" s="23" t="inlineStr">
@@ -25615,9 +25689,9 @@
           <t>蛇纹熊-伽勒尔</t>
         </is>
       </c>
-      <c r="C335" s="457" t="inlineStr">
-        <is>
-          <t>一般</t>
+      <c r="C335" s="664" t="inlineStr">
+        <is>
+          <t>恶/一般</t>
         </is>
       </c>
       <c r="D335" s="23" t="inlineStr">
@@ -25737,9 +25811,9 @@
           <t>直冲熊-伽勒尔</t>
         </is>
       </c>
-      <c r="C337" s="457" t="inlineStr">
-        <is>
-          <t>一般</t>
+      <c r="C337" s="664" t="inlineStr">
+        <is>
+          <t>恶/一般</t>
         </is>
       </c>
       <c r="D337" s="23" t="inlineStr">
@@ -31101,9 +31175,9 @@
           <t>飘浮泡泡-太阳</t>
         </is>
       </c>
-      <c r="C425" s="457" t="inlineStr">
-        <is>
-          <t>一般</t>
+      <c r="C425" s="450" t="inlineStr">
+        <is>
+          <t>火</t>
         </is>
       </c>
       <c r="D425" s="23" t="inlineStr">
@@ -31162,9 +31236,9 @@
           <t>飘浮泡泡-雨水</t>
         </is>
       </c>
-      <c r="C426" s="457" t="inlineStr">
-        <is>
-          <t>一般</t>
+      <c r="C426" s="452" t="inlineStr">
+        <is>
+          <t>水</t>
         </is>
       </c>
       <c r="D426" s="23" t="inlineStr">
@@ -31223,9 +31297,9 @@
           <t>飘浮泡泡-雪云</t>
         </is>
       </c>
-      <c r="C427" s="457" t="inlineStr">
-        <is>
-          <t>一般</t>
+      <c r="C427" s="540" t="inlineStr">
+        <is>
+          <t>冰</t>
         </is>
       </c>
       <c r="D427" s="23" t="inlineStr">
@@ -42410,9 +42484,9 @@
           <t>大剑鬼-洗翠</t>
         </is>
       </c>
-      <c r="C614" s="452" t="inlineStr">
-        <is>
-          <t>水</t>
+      <c r="C614" s="533" t="inlineStr">
+        <is>
+          <t>水/恶</t>
         </is>
       </c>
       <c r="D614" s="23" t="inlineStr">
@@ -45277,9 +45351,9 @@
           <t>裙儿小姐-洗翠</t>
         </is>
       </c>
-      <c r="C661" s="477" t="inlineStr">
-        <is>
-          <t>草</t>
+      <c r="C661" s="526" t="inlineStr">
+        <is>
+          <t>草/格斗</t>
         </is>
       </c>
       <c r="D661" s="23" t="inlineStr">
@@ -45765,9 +45839,9 @@
           <t>火红不倒翁-伽勒尔</t>
         </is>
       </c>
-      <c r="C669" s="450" t="inlineStr">
-        <is>
-          <t>火</t>
+      <c r="C669" s="540" t="inlineStr">
+        <is>
+          <t>冰</t>
         </is>
       </c>
       <c r="D669" s="23" t="inlineStr">
@@ -45887,9 +45961,9 @@
           <t>达摩狒狒-伽勒尔</t>
         </is>
       </c>
-      <c r="C671" s="450" t="inlineStr">
-        <is>
-          <t>火</t>
+      <c r="C671" s="540" t="inlineStr">
+        <is>
+          <t>冰</t>
         </is>
       </c>
       <c r="D671" s="23" t="inlineStr">
@@ -45978,19 +46052,19 @@
         <v>105</v>
       </c>
       <c r="J672" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="K672" s="23" t="n">
+        <v>105</v>
+      </c>
+      <c r="L672" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="K672" s="23" t="n">
+      <c r="M672" s="23" t="n">
+        <v>105</v>
+      </c>
+      <c r="N672" s="23" t="n">
         <v>55</v>
-      </c>
-      <c r="L672" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="M672" s="23" t="n">
-        <v>55</v>
-      </c>
-      <c r="N672" s="23" t="n">
-        <v>95</v>
       </c>
       <c r="O672" s="23" t="inlineStr">
         <is>
@@ -46497,9 +46571,9 @@
           <t>哭哭面具-伽勒尔</t>
         </is>
       </c>
-      <c r="C681" s="501" t="inlineStr">
-        <is>
-          <t>幽灵</t>
+      <c r="C681" s="599" t="inlineStr">
+        <is>
+          <t>地面/幽灵</t>
         </is>
       </c>
       <c r="D681" s="23" t="inlineStr">
@@ -47046,9 +47120,9 @@
           <t>索罗亚-洗翠</t>
         </is>
       </c>
-      <c r="C690" s="499" t="inlineStr">
-        <is>
-          <t>恶</t>
+      <c r="C690" s="720" t="inlineStr">
+        <is>
+          <t>一般/幽灵</t>
         </is>
       </c>
       <c r="D690" s="23" t="inlineStr">
@@ -47168,9 +47242,9 @@
           <t>索罗亚克-洗翠</t>
         </is>
       </c>
-      <c r="C692" s="499" t="inlineStr">
-        <is>
-          <t>恶</t>
+      <c r="C692" s="720" t="inlineStr">
+        <is>
+          <t>一般/幽灵</t>
         </is>
       </c>
       <c r="D692" s="23" t="inlineStr">
@@ -50462,9 +50536,9 @@
           <t>泥巴鱼-伽勒尔</t>
         </is>
       </c>
-      <c r="C746" s="598" t="inlineStr">
-        <is>
-          <t>地面/电</t>
+      <c r="C746" s="586" t="inlineStr">
+        <is>
+          <t>地面/钢</t>
         </is>
       </c>
       <c r="D746" s="23" t="inlineStr">
@@ -51133,9 +51207,9 @@
           <t>勇士雄鹰-洗翠</t>
         </is>
       </c>
-      <c r="C757" s="456" t="inlineStr">
-        <is>
-          <t>一般/飞行</t>
+      <c r="C757" s="494" t="inlineStr">
+        <is>
+          <t>超能/飞行</t>
         </is>
       </c>
       <c r="D757" s="23" t="inlineStr">
@@ -53405,19 +53479,19 @@
         <v>72</v>
       </c>
       <c r="J795" s="23" t="n">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="K795" s="23" t="n">
         <v>67</v>
       </c>
       <c r="L795" s="23" t="n">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="M795" s="23" t="n">
         <v>71</v>
       </c>
       <c r="N795" s="23" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="O795" s="23" t="inlineStr">
         <is>
@@ -58804,9 +58878,9 @@
           <t>黏美儿-洗翠</t>
         </is>
       </c>
-      <c r="C884" s="489" t="inlineStr">
-        <is>
-          <t>龙</t>
+      <c r="C884" s="669" t="inlineStr">
+        <is>
+          <t>钢/龙</t>
         </is>
       </c>
       <c r="D884" s="23" t="inlineStr">
@@ -58926,9 +59000,9 @@
           <t>黏美龙-洗翠</t>
         </is>
       </c>
-      <c r="C886" s="489" t="inlineStr">
-        <is>
-          <t>龙</t>
+      <c r="C886" s="669" t="inlineStr">
+        <is>
+          <t>钢/龙</t>
         </is>
       </c>
       <c r="D886" s="23" t="inlineStr">
@@ -59414,9 +59488,9 @@
           <t>冰岩怪-洗翠</t>
         </is>
       </c>
-      <c r="C894" s="540" t="inlineStr">
-        <is>
-          <t>冰</t>
+      <c r="C894" s="721" t="inlineStr">
+        <is>
+          <t>冰/岩石</t>
         </is>
       </c>
       <c r="D894" s="23" t="inlineStr">
